--- a/Result/profitability/3663.xlsx
+++ b/Result/profitability/3663.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.18125</v>
+        <v>0.18</v>
       </c>
       <c r="N2" t="n">
-        <v>5.0325</v>
+        <v>4.6825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>0.27</v>
+        <v>0.245</v>
       </c>
       <c r="N3" t="n">
-        <v>5.06875</v>
+        <v>4.68</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.25125</v>
+        <v>0.2425</v>
       </c>
       <c r="N4" t="n">
-        <v>4.96375</v>
+        <v>4.595</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0.32125</v>
+        <v>0.3375</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8725</v>
+        <v>4.7675</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.47625</v>
+        <v>0.4849999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>5.17375</v>
+        <v>5.27375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.63375</v>
+        <v>0.63625</v>
       </c>
       <c r="N7" t="n">
-        <v>5.715</v>
+        <v>5.7875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>99.40000000000001</v>
@@ -9070,6 +9070,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1647</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1591</v>
+      </c>
+      <c r="E69" t="n">
+        <v>56</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.05749999999999997</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4.67125</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.9230769230769231</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.3416988416988417</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-1.181818181818182</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-0.8399999999999999</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.1976470588235294</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
